--- a/branches/master/StructureDefinition-hiv-med-req.xlsx
+++ b/branches/master/StructureDefinition-hiv-med-req.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T06:27:52+00:00</t>
+    <t>2023-05-05T18:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-med-req.xlsx
+++ b/branches/master/StructureDefinition-hiv-med-req.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:20+00:00</t>
+    <t>2023-05-05T18:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
